--- a/buy-zapchasti-toyota-camry-2018.xlsx
+++ b/buy-zapchasti-toyota-camry-2018.xlsx
@@ -7,13 +7,14 @@
     <sheet sheetId="1" name="Дашборд" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Прайс" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Источники" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="О прайсе" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="176">
   <si>
     <t>Сводка по бу-запчастям Toyota Camry XV70 2018</t>
   </si>
@@ -517,6 +518,30 @@
   </si>
   <si>
     <t>Компактная электрика и навесное</t>
+  </si>
+  <si>
+    <t>ExcelPrice — цены на любые запчасти</t>
+  </si>
+  <si>
+    <t>Полные прайс-листы по моделям авто: все запчасти + актуальные цены со всего интернета</t>
+  </si>
+  <si>
+    <t>Заказать свой прайс: https://excelprice.ru</t>
+  </si>
+  <si>
+    <t>Контакты:</t>
+  </si>
+  <si>
+    <t>Telegram: @Excelprice</t>
+  </si>
+  <si>
+    <t>WhatsApp: +7 (900) 000-44-69</t>
+  </si>
+  <si>
+    <t>Email: dot.akc@yandex.ru</t>
+  </si>
+  <si>
+    <t>Если этот файл вам прислали — вы можете заказать такой же прайс на свою модель на сайте excelprice.ru</t>
   </si>
 </sst>
 </file>
@@ -527,7 +552,7 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;;[Red]-#,##0&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,6 +612,35 @@
       <color rgb="FF2A7F77"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF2F5597"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF667085"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="13"/>
+      <color rgb="FF2A7F77"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2A37"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF667085"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -643,7 +697,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -686,6 +740,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1315,22 +1374,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{92DC2AC5-B1C2-48EB-B45F-2D87E8D6771F}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E10:E16</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2755,7 +2799,7 @@
     <hyperlink ref="K38" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2924,6 +2968,66 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="A7" r:id="rId2"/>
+    <hyperlink ref="A8" r:id="rId3"/>
+    <hyperlink ref="A9" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>